--- a/data/trans_orig/P36BPD06_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD06_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de raciones de mantequilla, margarina o nata que consume al día en 2023</t>
+          <t>Población según el número de raciones de mantequilla, margarina o nata que consume al día en 2023 (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>67871</t>
+          <t>70664</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>128694</t>
+          <t>129014</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>59501</t>
+          <t>59215</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>98174</t>
+          <t>98622</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>141080</t>
+          <t>145153</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>209880</t>
+          <t>210423</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,5%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>271293</t>
+          <t>270973</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>332116</t>
+          <t>329323</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>215026</t>
+          <t>214578</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>253699</t>
+          <t>253985</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>503307</t>
+          <t>502764</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>572107</t>
+          <t>568034</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>79,65%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82364</t>
+          <t>80960</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>124994</t>
+          <t>125239</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>122372</t>
+          <t>121999</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>304825</t>
+          <t>310930</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>60,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>219981</t>
+          <t>221340</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>445149</t>
+          <t>453753</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>48,6%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>297192</t>
+          <t>296947</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>339822</t>
+          <t>341226</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>206679</t>
+          <t>200574</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>389132</t>
+          <t>389505</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>488541</t>
+          <t>479937</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>713709</t>
+          <t>712350</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>76,29%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>103169</t>
+          <t>104340</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>144709</t>
+          <t>143242</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>117704</t>
+          <t>117241</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>149895</t>
+          <t>151067</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>233053</t>
+          <t>231814</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>285334</t>
+          <t>282539</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,27%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>389044</t>
+          <t>390511</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>430584</t>
+          <t>429413</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>391754</t>
+          <t>390582</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>423945</t>
+          <t>424408</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>78,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>790068</t>
+          <t>792863</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>842349</t>
+          <t>843588</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,44%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65673</t>
+          <t>58220</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>203885</t>
+          <t>204534</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>124348</t>
+          <t>126220</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>170211</t>
+          <t>171009</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>173151</t>
+          <t>175823</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>351198</t>
+          <t>353909</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,16%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>681653</t>
+          <t>681004</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>819865</t>
+          <t>827318</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>541223</t>
+          <t>540425</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>587086</t>
+          <t>585214</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1245774</t>
+          <t>1243063</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1423821</t>
+          <t>1421149</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>88,99%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>110269</t>
+          <t>109324</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>146682</t>
+          <t>147118</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>113716</t>
+          <t>115275</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>145477</t>
+          <t>145612</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>234043</t>
+          <t>233767</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>284316</t>
+          <t>281263</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,49%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>409666</t>
+          <t>409230</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>446079</t>
+          <t>447024</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>401639</t>
+          <t>401504</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>433400</t>
+          <t>431841</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>819148</t>
+          <t>822201</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>869421</t>
+          <t>869697</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,82%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>72674</t>
+          <t>73239</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>98286</t>
+          <t>98597</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>140480</t>
+          <t>139426</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>476404</t>
+          <t>479308</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>223707</t>
+          <t>224330</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>659481</t>
+          <t>679943</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>69,88%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>266925</t>
+          <t>266614</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>292537</t>
+          <t>291972</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>131402</t>
+          <t>128498</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>467326</t>
+          <t>468380</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>313536</t>
+          <t>293074</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>749310</t>
+          <t>748687</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>76,94%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>54287</t>
+          <t>55927</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>77794</t>
+          <t>77609</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>79032</t>
+          <t>80679</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>105028</t>
+          <t>105220</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>144035</t>
+          <t>141796</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>175976</t>
+          <t>174617</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,71%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>204574</t>
+          <t>204759</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>228081</t>
+          <t>226441</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>72,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>319326</t>
+          <t>319134</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>345322</t>
+          <t>343675</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>530746</t>
+          <t>532105</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>562687</t>
+          <t>564926</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>79,94%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>580597</t>
+          <t>582424</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>824014</t>
+          <t>821203</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>879135</t>
+          <t>866545</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1570904</t>
+          <t>1559226</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1562250</t>
+          <t>1589899</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2291013</t>
+          <t>2362623</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>33,26%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2621376</t>
+          <t>2624187</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2864793</t>
+          <t>2862966</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2086159</t>
+          <t>2097837</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2777928</t>
+          <t>2790518</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4811440</t>
+          <t>4739830</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5540203</t>
+          <t>5512554</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>77,61%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD06_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD06_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>96417</t>
+          <t>111872</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>70664</t>
+          <t>87039</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>129014</t>
+          <t>141322</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>77343</t>
+          <t>95683</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>59215</t>
+          <t>75482</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>98622</t>
+          <t>121625</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>173760</t>
+          <t>207555</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>145153</t>
+          <t>174487</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>210423</t>
+          <t>242694</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>31,51%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>303570</t>
+          <t>295921</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>270973</t>
+          <t>266471</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>329323</t>
+          <t>320754</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>235857</t>
+          <t>266829</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>214578</t>
+          <t>240887</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>253985</t>
+          <t>287030</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>539427</t>
+          <t>562750</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>502764</t>
+          <t>527611</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>568034</t>
+          <t>595818</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>77,35%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>102031</t>
+          <t>119523</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>80960</t>
+          <t>96290</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>125239</t>
+          <t>144483</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>181037</t>
+          <t>127965</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>121999</t>
+          <t>108099</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>310930</t>
+          <t>148075</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>283068</t>
+          <t>247488</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>221340</t>
+          <t>217956</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>453753</t>
+          <t>282050</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>28,88%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>320155</t>
+          <t>356008</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>296947</t>
+          <t>331048</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>341226</t>
+          <t>379241</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>69,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>330467</t>
+          <t>373118</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>200574</t>
+          <t>353008</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>389505</t>
+          <t>392984</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>650622</t>
+          <t>729126</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>479937</t>
+          <t>694564</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>712350</t>
+          <t>758658</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>77,68%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>422186</t>
+          <t>475531</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>422186</t>
+          <t>475531</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>422186</t>
+          <t>475531</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>933690</t>
+          <t>976614</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>933690</t>
+          <t>976614</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>933690</t>
+          <t>976614</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>123808</t>
+          <t>152574</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>104340</t>
+          <t>129766</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>143242</t>
+          <t>176776</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>133369</t>
+          <t>155583</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>117241</t>
+          <t>138646</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>151067</t>
+          <t>175718</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>257177</t>
+          <t>308157</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>231814</t>
+          <t>281486</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>282539</t>
+          <t>341748</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>27,61%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>409945</t>
+          <t>464556</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>390511</t>
+          <t>440354</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>429413</t>
+          <t>487364</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>71,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>408280</t>
+          <t>465131</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>390582</t>
+          <t>444996</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>424408</t>
+          <t>482068</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>818225</t>
+          <t>929687</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>792863</t>
+          <t>896096</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>843588</t>
+          <t>956358</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>77,26%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>533753</t>
+          <t>617130</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>533753</t>
+          <t>617130</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>533753</t>
+          <t>617130</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>541649</t>
+          <t>620714</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>541649</t>
+          <t>620714</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>541649</t>
+          <t>620714</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1075402</t>
+          <t>1237844</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1075402</t>
+          <t>1237844</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1075402</t>
+          <t>1237844</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>138878</t>
+          <t>155664</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58220</t>
+          <t>133781</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>204534</t>
+          <t>179550</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>150179</t>
+          <t>168671</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>126220</t>
+          <t>151366</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>171009</t>
+          <t>188560</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>289057</t>
+          <t>324334</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>175823</t>
+          <t>294171</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>353909</t>
+          <t>353415</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>24,65%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>746660</t>
+          <t>542774</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>681004</t>
+          <t>518888</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>827318</t>
+          <t>564657</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>561255</t>
+          <t>566692</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>540425</t>
+          <t>546803</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>585214</t>
+          <t>583997</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1307915</t>
+          <t>1109466</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1243063</t>
+          <t>1080385</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1421149</t>
+          <t>1139629</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>79,48%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>885538</t>
+          <t>698438</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>885538</t>
+          <t>698438</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>885538</t>
+          <t>698438</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>711434</t>
+          <t>735363</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>711434</t>
+          <t>735363</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>711434</t>
+          <t>735363</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1596972</t>
+          <t>1433800</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1596972</t>
+          <t>1433800</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1596972</t>
+          <t>1433800</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>127685</t>
+          <t>138091</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>109324</t>
+          <t>119362</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>147118</t>
+          <t>158538</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>129698</t>
+          <t>147267</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>115275</t>
+          <t>130903</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>145612</t>
+          <t>164636</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>257383</t>
+          <t>285358</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>233767</t>
+          <t>260604</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>281263</t>
+          <t>311146</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,68%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>428663</t>
+          <t>466209</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>409230</t>
+          <t>445762</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>447024</t>
+          <t>484938</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>417418</t>
+          <t>460293</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>401504</t>
+          <t>442924</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>431841</t>
+          <t>476657</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>846081</t>
+          <t>926502</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>822201</t>
+          <t>900714</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>869697</t>
+          <t>951256</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>78,5%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>556348</t>
+          <t>604300</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>556348</t>
+          <t>604300</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>556348</t>
+          <t>604300</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547116</t>
+          <t>607560</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547116</t>
+          <t>607560</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547116</t>
+          <t>607560</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1103464</t>
+          <t>1211860</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1103464</t>
+          <t>1211860</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1103464</t>
+          <t>1211860</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>85611</t>
+          <t>95127</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>73239</t>
+          <t>81510</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>98597</t>
+          <t>109112</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>302333</t>
+          <t>110837</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>139426</t>
+          <t>98675</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>479308</t>
+          <t>125303</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>387944</t>
+          <t>205964</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>224330</t>
+          <t>186016</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>679943</t>
+          <t>224007</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>26,59%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>279600</t>
+          <t>308721</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>266614</t>
+          <t>294736</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>291972</t>
+          <t>322338</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>305473</t>
+          <t>327757</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>128498</t>
+          <t>313291</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>468380</t>
+          <t>339919</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>585073</t>
+          <t>636478</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>293074</t>
+          <t>618435</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>748687</t>
+          <t>656426</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>77,92%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>365211</t>
+          <t>403848</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>365211</t>
+          <t>403848</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>365211</t>
+          <t>403848</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>607806</t>
+          <t>438594</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>607806</t>
+          <t>438594</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>607806</t>
+          <t>438594</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>973017</t>
+          <t>842442</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>973017</t>
+          <t>842442</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>973017</t>
+          <t>842442</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>66176</t>
+          <t>72341</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>55927</t>
+          <t>60859</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>77609</t>
+          <t>85642</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>92046</t>
+          <t>103476</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>80679</t>
+          <t>90049</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>105220</t>
+          <t>117557</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>158222</t>
+          <t>175817</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>141796</t>
+          <t>156385</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>174617</t>
+          <t>193042</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,98%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>216192</t>
+          <t>237438</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>204759</t>
+          <t>224137</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>226441</t>
+          <t>248920</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>332308</t>
+          <t>359614</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>319134</t>
+          <t>345533</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>343675</t>
+          <t>373041</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>548500</t>
+          <t>597051</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>532105</t>
+          <t>579826</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>564926</t>
+          <t>616483</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>79,77%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282368</t>
+          <t>309779</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282368</t>
+          <t>309779</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282368</t>
+          <t>309779</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>424354</t>
+          <t>463090</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>424354</t>
+          <t>463090</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>424354</t>
+          <t>463090</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>706722</t>
+          <t>772868</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>706722</t>
+          <t>772868</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>706722</t>
+          <t>772868</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>740606</t>
+          <t>845192</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>582424</t>
+          <t>787103</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>821203</t>
+          <t>901671</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1066004</t>
+          <t>909481</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>866545</t>
+          <t>866526</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1559226</t>
+          <t>957580</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1806611</t>
+          <t>1754674</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1589899</t>
+          <t>1681482</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2362623</t>
+          <t>1829631</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>25,25%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2704784</t>
+          <t>2671626</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2624187</t>
+          <t>2615147</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2862966</t>
+          <t>2729715</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2591059</t>
+          <t>2819434</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2097837</t>
+          <t>2771335</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2790518</t>
+          <t>2862389</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>5295842</t>
+          <t>5491060</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4739830</t>
+          <t>5416103</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5512554</t>
+          <t>5564252</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>76,79%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3445390</t>
+          <t>3516818</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3445390</t>
+          <t>3516818</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3445390</t>
+          <t>3516818</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3657063</t>
+          <t>3728915</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3657063</t>
+          <t>3728915</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3657063</t>
+          <t>3728915</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7102453</t>
+          <t>7245734</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7102453</t>
+          <t>7245734</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7102453</t>
+          <t>7245734</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
